--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260425_202815.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260425_202815.xlsx
@@ -4902,7 +4902,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
